--- a/static/static_MP_PBHAPChems_withHHEquivalencyFactors.xlsx
+++ b/static/static_MP_PBHAPChems_withHHEquivalencyFactors.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\55586\Desktop\tools\access tool\access-tool-migration\static\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17475\Downloads\RTR2HEM_20231117\RTR2HEM\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528ECB4A-FB33-4DB9-A631-C3A33C6DE9FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F15136-916F-49A5-A750-3FE01674D4E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2835" yWindow="3450" windowWidth="23070" windowHeight="14910" xr2:uid="{52E24209-A632-4F75-AA55-147BF6C2EB93}"/>
+    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15840" xr2:uid="{52E24209-A632-4F75-AA55-147BF6C2EB93}"/>
   </bookViews>
   <sheets>
     <sheet name="static" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">static!$A$1:$J$55</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="88">
   <si>
     <t/>
   </si>
@@ -294,6 +297,12 @@
   </si>
   <si>
     <t>Chem Name For Tier 2 Tool</t>
+  </si>
+  <si>
+    <t>20231220</t>
+  </si>
+  <si>
+    <t>20231220: Updated TEF based on 2022 WHO reexamination of dioxin/furan toxicity (and updated REF accordingly). 20200421: updated EEF (and then REF) based on fixes to SMIRC air concentration and root concentration factors; 20210401: updated EEF (and then REF) based on corrected dairy IR for adults.</t>
   </si>
 </sst>
 </file>
@@ -319,12 +328,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -384,17 +395,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -712,62 +722,54 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16D29CCF-2625-4306-80FC-3317DF5D9A47}">
   <dimension ref="A1:J55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="38.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="34.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="29" style="1" customWidth="1"/>
-    <col min="4" max="4" width="52.28515625" style="1" customWidth="1"/>
-    <col min="5" max="7" width="21.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="27" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9235.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="69.5703125" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="16384" width="38.5703125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>74</v>
       </c>
       <c r="E2" s="3">
@@ -779,27 +781,27 @@
       <c r="G2" s="3">
         <v>1</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="I2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="3">
@@ -811,27 +813,27 @@
       <c r="G3" s="3">
         <v>0.15652476032218601</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="H3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="B4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="3">
@@ -843,27 +845,27 @@
       <c r="G4" s="3">
         <v>2.5146033259982301E-2</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="H4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E5" s="3">
@@ -875,27 +877,27 @@
       <c r="G5" s="3">
         <v>0</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I5" s="2" t="s">
+      <c r="H5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="J5" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="B6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E6" s="3">
@@ -907,27 +909,27 @@
       <c r="G6" s="3">
         <v>0.15652476032218601</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="H6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="B7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E7" s="3">
@@ -939,27 +941,27 @@
       <c r="G7" s="3">
         <v>0</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I7" s="2" t="s">
+      <c r="H7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="J7" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="3">
@@ -971,347 +973,345 @@
       <c r="G8" s="3">
         <v>0.104570922246389</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="H8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E9" s="3">
-        <v>2.9999999999999997E-4</v>
+        <v>2E-3</v>
       </c>
       <c r="F9" s="3">
-        <v>0.46269670756467701</v>
+        <v>0.46269670756467746</v>
       </c>
       <c r="G9" s="3">
-        <v>1.3880901226940299E-4</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J9" s="2" t="s">
+        <v>9.2539341512935499E-4</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E10" s="3">
-        <v>2.9999999999999997E-4</v>
+        <v>1E-3</v>
       </c>
       <c r="F10" s="3">
-        <v>0.74503941071549395</v>
+        <v>0.74503941071549418</v>
       </c>
       <c r="G10" s="3">
-        <v>2.23511823214648E-4</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J10" s="2" t="s">
+        <v>7.4503941071549424E-4</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E11" s="3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F11" s="3">
-        <v>3.2209717918635499</v>
+        <v>3.220971791863553</v>
       </c>
       <c r="G11" s="3">
-        <v>3.22097179186355E-2</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+        <v>6.4419435837271055E-2</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E12" s="3">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="F12" s="3">
-        <v>1.1770305800535901</v>
+        <v>1.1770305800535945</v>
       </c>
       <c r="G12" s="3">
-        <v>1.17703058005359E-2</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+        <v>5.8851529002679731E-2</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E13" s="3">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="F13" s="3">
-        <v>6.5070469296047202</v>
+        <v>6.5070469296047246</v>
       </c>
       <c r="G13" s="3">
-        <v>6.5070469296047206E-2</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+        <v>0.65070469296047251</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E14" s="3">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F14" s="3">
-        <v>1.2566071118412701</v>
+        <v>1.2566071118412694</v>
       </c>
       <c r="G14" s="3">
-        <v>0.125660711184127</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+        <v>0.3769821335523808</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E15" s="3">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F15" s="3">
-        <v>1.30096528626089</v>
+        <v>1.300965286260894</v>
       </c>
       <c r="G15" s="3">
-        <v>0.130096528626089</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+        <v>0.11708687576348045</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E16" s="3">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F16" s="3">
-        <v>0.31292304573124902</v>
+        <v>0.31292304573124913</v>
       </c>
       <c r="G16" s="3">
-        <v>3.1292304573124902E-2</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+        <v>2.8163074115812422E-2</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E17" s="3">
         <v>4.1333333333333298E-2</v>
       </c>
       <c r="F17" s="3">
-        <v>0.61852386990596098</v>
+        <v>0.61852386990596142</v>
       </c>
       <c r="G17" s="3">
-        <v>2.5565653289446402E-2</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I17" s="2" t="s">
+        <v>2.5565653289446384E-2</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="J17" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="J17" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E18" s="3">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F18" s="3">
-        <v>0.58105762184633103</v>
+        <v>0.58105762184633125</v>
       </c>
       <c r="G18" s="3">
-        <v>5.8105762184633099E-2</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+        <v>0.11621152436926625</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E19" s="3">
@@ -1321,93 +1321,93 @@
         <v>0.61896628781930696</v>
       </c>
       <c r="G19" s="3">
-        <v>2.5583939896531301E-2</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I19" s="2" t="s">
+        <v>2.5583939896531332E-2</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="J19" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="J19" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E20" s="3">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="F20" s="3">
         <v>0.856998883945575</v>
       </c>
       <c r="G20" s="3">
-        <v>2.5709966518367201E-2</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+        <v>8.5699888394557503E-3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E21" s="3">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F21" s="3">
-        <v>1.8567765844931901</v>
+        <v>1.8567765844931894</v>
       </c>
       <c r="G21" s="3">
-        <v>1.8567765844931901</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+        <v>0.74271063379727575</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="2" t="s">
+      <c r="B22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E22" s="3">
@@ -1419,155 +1419,155 @@
       <c r="G22" s="3">
         <v>1.32810394210917E-4</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="H22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E23" s="3">
         <v>0.1</v>
       </c>
       <c r="F23" s="3">
-        <v>0.34283551828166497</v>
+        <v>0.34283551828166492</v>
       </c>
       <c r="G23" s="3">
-        <v>3.4283551828166503E-2</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I23" s="2" t="s">
+        <v>3.4283551828166496E-2</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="J23" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="J23" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E24" s="3">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F24" s="3">
-        <v>1.09203556075153</v>
+        <v>1.0920355607515293</v>
       </c>
       <c r="G24" s="3">
-        <v>0.32761066822545898</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I24" s="2" t="s">
+        <v>0.10920355607515293</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" s="3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0.67096378887367947</v>
+      </c>
+      <c r="G25" s="3">
+        <v>4.6967465221157564E-2</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1</v>
+      </c>
+      <c r="G26" s="3">
+        <v>1</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="J24" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E25" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="F25" s="3">
-        <v>0.67096378887367902</v>
-      </c>
-      <c r="G25" s="3">
-        <v>6.7096378887367997E-2</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26" s="3">
-        <v>1</v>
-      </c>
-      <c r="F26" s="3">
-        <v>1</v>
-      </c>
-      <c r="G26" s="3">
-        <v>1</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="J26" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D27" s="2" t="s">
+      <c r="B27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E27" s="3">
@@ -1579,27 +1579,27 @@
       <c r="G27" s="3">
         <v>5.4507786476011902E-4</v>
       </c>
-      <c r="H27" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="H27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="B28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E28" s="3">
@@ -1611,27 +1611,27 @@
       <c r="G28" s="3">
         <v>1.32271053236461E-4</v>
       </c>
-      <c r="H28" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+      <c r="H28" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29" s="2" t="s">
+      <c r="B29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E29" s="3">
@@ -1643,27 +1643,27 @@
       <c r="G29" s="3">
         <v>55.5406040836817</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+      <c r="H29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D30" s="2" t="s">
+      <c r="B30" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E30" s="3">
@@ -1675,27 +1675,27 @@
       <c r="G30" s="3">
         <v>299.644422413781</v>
       </c>
-      <c r="H30" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+      <c r="H30" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D31" s="2" t="s">
+      <c r="B31" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E31" s="3">
@@ -1707,27 +1707,27 @@
       <c r="G31" s="3">
         <v>1.8872269000192899E-4</v>
       </c>
-      <c r="H31" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
+      <c r="H31" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D32" s="2" t="s">
+      <c r="B32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E32" s="3">
@@ -1739,27 +1739,27 @@
       <c r="G32" s="3">
         <v>2.86829741789905E-4</v>
       </c>
-      <c r="H32" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+      <c r="H32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D33" s="2" t="s">
+      <c r="B33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E33" s="3">
@@ -1771,27 +1771,27 @@
       <c r="G33" s="3">
         <v>0</v>
       </c>
-      <c r="H33" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I33" s="2" t="s">
+      <c r="H33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="J33" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E34" s="3">
@@ -1803,27 +1803,27 @@
       <c r="G34" s="3">
         <v>1</v>
       </c>
-      <c r="H34" s="2" t="s">
+      <c r="H34" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I34" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
+      <c r="I34" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D35" s="2" t="s">
+      <c r="B35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E35" s="3">
@@ -1835,27 +1835,27 @@
       <c r="G35" s="3">
         <v>6.7382990124237501E-3</v>
       </c>
-      <c r="H35" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+      <c r="H35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D36" s="2" t="s">
+      <c r="B36" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E36" s="3">
@@ -1867,27 +1867,27 @@
       <c r="G36" s="3">
         <v>5.4844813433337601E-2</v>
       </c>
-      <c r="H36" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I36" s="2" t="s">
+      <c r="H36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J36" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
+      <c r="J36" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D37" s="2" t="s">
+      <c r="B37" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E37" s="3">
@@ -1899,27 +1899,27 @@
       <c r="G37" s="3">
         <v>1.1223421341919001E-2</v>
       </c>
-      <c r="H37" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
+      <c r="H37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D38" s="2" t="s">
+      <c r="B38" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E38" s="3">
@@ -1931,27 +1931,27 @@
       <c r="G38" s="3">
         <v>0.13320306061435799</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
+      <c r="H38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" s="2" t="s">
+      <c r="B39" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E39" s="3">
@@ -1963,27 +1963,27 @@
       <c r="G39" s="3">
         <v>1.1223421341919001E-2</v>
       </c>
-      <c r="H39" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I39" s="2" t="s">
+      <c r="H39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J39" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
+      <c r="J39" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D40" s="2" t="s">
+      <c r="B40" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E40" s="3">
@@ -1995,27 +1995,27 @@
       <c r="G40" s="3">
         <v>0.141116130838182</v>
       </c>
-      <c r="H40" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
+      <c r="H40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D41" s="2" t="s">
+      <c r="B41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E41" s="3">
@@ -2027,27 +2027,27 @@
       <c r="G41" s="3">
         <v>1</v>
       </c>
-      <c r="H41" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
+      <c r="H41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D42" s="2" t="s">
+      <c r="B42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E42" s="3">
@@ -2059,27 +2059,27 @@
       <c r="G42" s="3">
         <v>0.34093902869455001</v>
       </c>
-      <c r="H42" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
+      <c r="H42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D43" s="2" t="s">
+      <c r="B43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E43" s="3">
@@ -2091,27 +2091,27 @@
       <c r="G43" s="3">
         <v>0.23923881189837601</v>
       </c>
-      <c r="H43" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
+      <c r="H43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D44" s="2" t="s">
+      <c r="B44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E44" s="3">
@@ -2123,27 +2123,27 @@
       <c r="G44" s="3">
         <v>5.2339245398583097E-2</v>
       </c>
-      <c r="H44" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
+      <c r="H44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D45" s="2" t="s">
+      <c r="B45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E45" s="3">
@@ -2155,27 +2155,27 @@
       <c r="G45" s="3">
         <v>0.26800682865776498</v>
       </c>
-      <c r="H45" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I45" s="2" t="s">
+      <c r="H45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I45" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J45" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
+      <c r="J45" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D46" s="2" t="s">
+      <c r="B46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E46" s="3">
@@ -2187,27 +2187,27 @@
       <c r="G46" s="3">
         <v>2.7449969256252701E-4</v>
       </c>
-      <c r="H46" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J46" s="2" t="s">
+      <c r="H46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J46" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E47" s="3">
@@ -2219,27 +2219,27 @@
       <c r="G47" s="3">
         <v>1</v>
       </c>
-      <c r="H47" s="2" t="s">
+      <c r="H47" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I47" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="J47" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
+      <c r="I47" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" s="2" t="s">
+      <c r="B48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E48" s="3">
@@ -2251,27 +2251,27 @@
       <c r="G48" s="3">
         <v>3.5491139875774899E-5</v>
       </c>
-      <c r="H48" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
+      <c r="H48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D49" s="2" t="s">
+      <c r="B49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E49" s="3">
@@ -2283,27 +2283,27 @@
       <c r="G49" s="3">
         <v>1.5612944662961401E-4</v>
       </c>
-      <c r="H49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I49" s="2" t="s">
+      <c r="H49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J49" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
+      <c r="J49" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D50" s="2" t="s">
+      <c r="B50" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E50" s="3">
@@ -2315,27 +2315,27 @@
       <c r="G50" s="3">
         <v>3.0172744112290598E-2</v>
       </c>
-      <c r="H50" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
+      <c r="H50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D51" s="2" t="s">
+      <c r="B51" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E51" s="3">
@@ -2347,27 +2347,27 @@
       <c r="G51" s="3">
         <v>3.8897967383981902</v>
       </c>
-      <c r="H51" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
+      <c r="H51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D52" s="2" t="s">
+      <c r="B52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E52" s="3">
@@ -2379,27 +2379,27 @@
       <c r="G52" s="3">
         <v>254.981112153276</v>
       </c>
-      <c r="H52" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J52" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
+      <c r="H52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D53" s="2" t="s">
+      <c r="B53" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E53" s="3">
@@ -2411,27 +2411,27 @@
       <c r="G53" s="3">
         <v>6.8459445108792099E-4</v>
       </c>
-      <c r="H53" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J53" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
+      <c r="H53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D54" s="2" t="s">
+      <c r="B54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E54" s="3">
@@ -2443,27 +2443,27 @@
       <c r="G54" s="3">
         <v>2.2356745294084199E-4</v>
       </c>
-      <c r="H54" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
+      <c r="H54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D55" s="2" t="s">
+      <c r="B55" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E55" s="3">
@@ -2475,17 +2475,18 @@
       <c r="G55" s="3">
         <v>0.28853143608465298</v>
       </c>
-      <c r="H55" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J55" s="2" t="s">
+      <c r="H55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J55" s="3" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J55" xr:uid="{16D29CCF-2625-4306-80FC-3317DF5D9A47}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>